--- a/results_(stress_test)_PCCxSigmoid-PLI-/cnn_evaluation(stress_test)_k-100_p-10_nm_basis-False_nm_modifier-False.xlsx
+++ b/results_(stress_test)_PCCxSigmoid-PLI-/cnn_evaluation(stress_test)_k-100_p-10_nm_basis-False_nm_modifier-False.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E33"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,609 +448,324 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>sub6ex1</t>
+          <t>sub1ex1</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>81.27449199387539</v>
+        <v>77.52696822636874</v>
       </c>
       <c r="C2" t="n">
-        <v>80.64829420176065</v>
+        <v>77.19992108351811</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5727143747343992</v>
+        <v>0.61235154994453</v>
       </c>
       <c r="E2" t="n">
-        <v>81.27449199387539</v>
+        <v>77.52696822636874</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>sub6ex2</t>
+          <t>sub1ex2</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>81.98885803510412</v>
+        <v>76.40169897663475</v>
       </c>
       <c r="C3" t="n">
-        <v>81.58383870316004</v>
+        <v>76.42661196793165</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5325864194581906</v>
+        <v>0.6403083541120093</v>
       </c>
       <c r="E3" t="n">
-        <v>81.98885803510412</v>
+        <v>76.40169897663475</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>sub6ex3</t>
+          <t>sub1ex3</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>83.63091376222977</v>
+        <v>67.29072050796287</v>
       </c>
       <c r="C4" t="n">
-        <v>82.96994428699732</v>
+        <v>66.84830314914068</v>
       </c>
       <c r="D4" t="n">
-        <v>0.4576803473134835</v>
+        <v>0.8296316348016262</v>
       </c>
       <c r="E4" t="n">
-        <v>83.63091376222977</v>
+        <v>67.29072050796287</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>sub7ex1</t>
+          <t>sub2ex1</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>79.11936954471925</v>
+        <v>77.67342278047389</v>
       </c>
       <c r="C5" t="n">
-        <v>79.31637055315312</v>
+        <v>76.81888860175167</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5135009800394376</v>
+        <v>0.6598786286388834</v>
       </c>
       <c r="E5" t="n">
-        <v>79.11936954471925</v>
+        <v>77.67342278047389</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>sub7ex2</t>
+          <t>sub2ex2</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>81.20961253990086</v>
+        <v>73.9353281602782</v>
       </c>
       <c r="C6" t="n">
-        <v>81.23683342375782</v>
+        <v>73.02152993150534</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4904759103509908</v>
+        <v>0.8865028914995492</v>
       </c>
       <c r="E6" t="n">
-        <v>81.20961253990086</v>
+        <v>73.9353281602782</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>sub7ex3</t>
+          <t>sub2ex3</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>74.16759660550697</v>
+        <v>75.26284829453542</v>
       </c>
       <c r="C7" t="n">
-        <v>73.51262775468921</v>
+        <v>74.66261404370678</v>
       </c>
       <c r="D7" t="n">
-        <v>0.668209808319807</v>
+        <v>0.5882732146730025</v>
       </c>
       <c r="E7" t="n">
-        <v>74.16759660550697</v>
+        <v>75.26284829453542</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>sub8ex1</t>
+          <t>sub3ex1</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>86.14105658353446</v>
+        <v>71.39179404666132</v>
       </c>
       <c r="C8" t="n">
-        <v>85.76343880912876</v>
+        <v>71.13625879188842</v>
       </c>
       <c r="D8" t="n">
-        <v>0.401227337376137</v>
+        <v>0.7740633031974237</v>
       </c>
       <c r="E8" t="n">
-        <v>86.14105658353446</v>
+        <v>71.3917940466613</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>sub8ex2</t>
+          <t>sub3ex2</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>87.64997967110443</v>
+        <v>79.88754227977751</v>
       </c>
       <c r="C9" t="n">
-        <v>87.69026365667432</v>
+        <v>79.10502667673987</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2995289520981411</v>
+        <v>0.5669198195139568</v>
       </c>
       <c r="E9" t="n">
-        <v>87.64997967110442</v>
+        <v>79.88754227977751</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>sub8ex3</t>
+          <t>sub3ex3</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>87.96979212622946</v>
+        <v>82.74561198626284</v>
       </c>
       <c r="C10" t="n">
-        <v>88.04453160830418</v>
+        <v>82.24727357475591</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2783024327519039</v>
+        <v>0.4465996289936204</v>
       </c>
       <c r="E10" t="n">
-        <v>87.96979212622946</v>
+        <v>82.74561198626286</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>sub9ex1</t>
+          <t>sub4ex1</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>87.43778060363844</v>
+        <v>74.93559632868796</v>
       </c>
       <c r="C11" t="n">
-        <v>87.2824120173413</v>
+        <v>74.51001037369878</v>
       </c>
       <c r="D11" t="n">
-        <v>0.368816715987244</v>
+        <v>0.7948281330366929</v>
       </c>
       <c r="E11" t="n">
-        <v>87.43778060363844</v>
+        <v>74.93559632868796</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>sub9ex2</t>
+          <t>sub4ex2</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>81.18651545428594</v>
+        <v>67.92273289561328</v>
       </c>
       <c r="C12" t="n">
-        <v>81.02467478844753</v>
+        <v>67.68951925592906</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5228346966207027</v>
+        <v>0.8202641325692337</v>
       </c>
       <c r="E12" t="n">
-        <v>81.18651545428594</v>
+        <v>67.92273289561328</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>sub9ex3</t>
+          <t>sub4ex3</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>85.20938762446042</v>
+        <v>72.02233583335496</v>
       </c>
       <c r="C13" t="n">
-        <v>84.38223422429884</v>
+        <v>71.70703649508295</v>
       </c>
       <c r="D13" t="n">
-        <v>0.496470853779465</v>
+        <v>0.7438667833805084</v>
       </c>
       <c r="E13" t="n">
-        <v>85.20938762446042</v>
+        <v>72.02233583335496</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>sub10ex1</t>
+          <t>sub5ex1</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>79.91669478109672</v>
+        <v>75.49278107942111</v>
       </c>
       <c r="C14" t="n">
-        <v>79.79057949926529</v>
+        <v>74.16708940801115</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4786803103983402</v>
+        <v>0.6797797705978155</v>
       </c>
       <c r="E14" t="n">
-        <v>79.91669478109672</v>
+        <v>75.49278107942111</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>sub10ex2</t>
+          <t>sub5ex2</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>74.93412572773121</v>
+        <v>73.7482158150157</v>
       </c>
       <c r="C15" t="n">
-        <v>74.35340215610536</v>
+        <v>73.26141705793317</v>
       </c>
       <c r="D15" t="n">
-        <v>0.6963434460262456</v>
+        <v>0.7345144886523485</v>
       </c>
       <c r="E15" t="n">
-        <v>74.9341257277312</v>
+        <v>73.7482158150157</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>sub10ex3</t>
+          <t>sub5ex3</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>76.31493352018616</v>
+        <v>71.42233064299865</v>
       </c>
       <c r="C16" t="n">
-        <v>76.16782732595172</v>
+        <v>71.79059038262619</v>
       </c>
       <c r="D16" t="n">
-        <v>0.6559743347888192</v>
+        <v>0.7985936392719547</v>
       </c>
       <c r="E16" t="n">
-        <v>76.31493352018616</v>
+        <v>71.42233064299865</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>sub11ex1</t>
+          <t>Average</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>82.12873813787317</v>
+        <v>74.51066185693649</v>
       </c>
       <c r="C17" t="n">
-        <v>81.93874104046485</v>
+        <v>74.03947271961466</v>
       </c>
       <c r="D17" t="n">
-        <v>0.504057502746582</v>
+        <v>0.7050917315255436</v>
       </c>
       <c r="E17" t="n">
-        <v>82.12873813787317</v>
+        <v>74.51066185693649</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>sub11ex2</t>
+          <t>Std</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>84.69735897369354</v>
+        <v>4.02501285464775</v>
       </c>
       <c r="C18" t="n">
-        <v>84.38519753198048</v>
+        <v>3.91295827912665</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4268309714427839</v>
+        <v>0.115656141341837</v>
       </c>
       <c r="E18" t="n">
-        <v>84.69735897369354</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>sub11ex3</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>87.29426725144681</v>
-      </c>
-      <c r="C19" t="n">
-        <v>87.38137921330478</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0.3402867190539837</v>
-      </c>
-      <c r="E19" t="n">
-        <v>87.29426725144681</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>sub12ex1</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>76.20507097812265</v>
-      </c>
-      <c r="C20" t="n">
-        <v>75.37902356065696</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0.661706385264794</v>
-      </c>
-      <c r="E20" t="n">
-        <v>76.20507097812265</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>sub12ex2</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>71.30347148331734</v>
-      </c>
-      <c r="C21" t="n">
-        <v>70.173178219589</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0.8296771266808113</v>
-      </c>
-      <c r="E21" t="n">
-        <v>71.30347148331732</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>sub12ex3</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>79.27222553828321</v>
-      </c>
-      <c r="C22" t="n">
-        <v>78.80232839115919</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0.582902893749997</v>
-      </c>
-      <c r="E22" t="n">
-        <v>79.27222553828321</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>sub13ex1</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>80.29965657142364</v>
-      </c>
-      <c r="C23" t="n">
-        <v>80.04866981179906</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0.5554070632904768</v>
-      </c>
-      <c r="E23" t="n">
-        <v>80.29965657142364</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>sub13ex2</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>85.16691320859177</v>
-      </c>
-      <c r="C24" t="n">
-        <v>85.14560458068954</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0.4189289839230089</v>
-      </c>
-      <c r="E24" t="n">
-        <v>85.16691320859177</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>sub13ex3</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>82.92848554053236</v>
-      </c>
-      <c r="C25" t="n">
-        <v>82.2265461000969</v>
-      </c>
-      <c r="D25" t="n">
-        <v>0.4446711851283908</v>
-      </c>
-      <c r="E25" t="n">
-        <v>82.92848554053236</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>sub14ex1</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>82.53687315634218</v>
-      </c>
-      <c r="C26" t="n">
-        <v>82.34596391350688</v>
-      </c>
-      <c r="D26" t="n">
-        <v>0.4266851280195018</v>
-      </c>
-      <c r="E26" t="n">
-        <v>82.53687315634218</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>sub14ex2</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>73.75738544451076</v>
-      </c>
-      <c r="C27" t="n">
-        <v>73.63538060429008</v>
-      </c>
-      <c r="D27" t="n">
-        <v>0.7133977035370965</v>
-      </c>
-      <c r="E27" t="n">
-        <v>73.75738544451076</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>sub14ex3</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>77.82178046522894</v>
-      </c>
-      <c r="C28" t="n">
-        <v>77.20333062969543</v>
-      </c>
-      <c r="D28" t="n">
-        <v>0.6118848976989587</v>
-      </c>
-      <c r="E28" t="n">
-        <v>77.82178046522894</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>sub15ex1</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>88.88009411846124</v>
-      </c>
-      <c r="C29" t="n">
-        <v>88.96090106807955</v>
-      </c>
-      <c r="D29" t="n">
-        <v>0.3147946306038648</v>
-      </c>
-      <c r="E29" t="n">
-        <v>88.88009411846123</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>sub15ex2</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>90.33763267848337</v>
-      </c>
-      <c r="C30" t="n">
-        <v>90.23788704984989</v>
-      </c>
-      <c r="D30" t="n">
-        <v>0.2921223416187179</v>
-      </c>
-      <c r="E30" t="n">
-        <v>90.33763267848337</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>sub15ex3</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>90.30415488023252</v>
-      </c>
-      <c r="C31" t="n">
-        <v>89.66308652363206</v>
-      </c>
-      <c r="D31" t="n">
-        <v>0.3079171318095177</v>
-      </c>
-      <c r="E31" t="n">
-        <v>90.30415488023252</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Average</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>82.03617390000491</v>
-      </c>
-      <c r="C32" t="n">
-        <v>81.70981637492768</v>
-      </c>
-      <c r="D32" t="n">
-        <v>0.4954872528203931</v>
-      </c>
-      <c r="E32" t="n">
-        <v>82.03617390000491</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Std</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>5.037468419093506</v>
-      </c>
-      <c r="C33" t="n">
-        <v>5.182298637881426</v>
-      </c>
-      <c r="D33" t="n">
-        <v>0.1389724701635962</v>
-      </c>
-      <c r="E33" t="n">
-        <v>5.037468419093506</v>
+        <v>4.025012854647753</v>
       </c>
     </row>
   </sheetData>
@@ -1096,16 +811,16 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>82.03617390000491</v>
+        <v>74.51066185693649</v>
       </c>
       <c r="B2" t="n">
-        <v>81.70981637492768</v>
+        <v>74.03947271961466</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4954872528203931</v>
+        <v>0.7050917315255436</v>
       </c>
       <c r="D2" t="n">
-        <v>82.03617390000491</v>
+        <v>74.51066185693649</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -1115,16 +830,16 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>5.037468419093506</v>
+        <v>4.02501285464775</v>
       </c>
       <c r="B3" t="n">
-        <v>5.182298637881426</v>
+        <v>3.91295827912665</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1389724701635962</v>
+        <v>0.115656141341837</v>
       </c>
       <c r="D3" t="n">
-        <v>5.037468419093506</v>
+        <v>4.025012854647753</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -1190,28 +905,28 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>82.03617390000491</v>
+        <v>74.51066185693649</v>
       </c>
       <c r="B2" t="n">
-        <v>5.037468419093506</v>
+        <v>4.02501285464775</v>
       </c>
       <c r="C2" t="n">
-        <v>81.70981637492768</v>
+        <v>74.03947271961466</v>
       </c>
       <c r="D2" t="n">
-        <v>5.182298637881426</v>
+        <v>3.91295827912665</v>
       </c>
       <c r="E2" t="n">
-        <v>82.03617390000491</v>
+        <v>74.51066185693649</v>
       </c>
       <c r="F2" t="n">
-        <v>5.037468419093506</v>
+        <v>4.025012854647753</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4954872528203931</v>
+        <v>0.7050917315255436</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1389724701635962</v>
+        <v>0.115656141341837</v>
       </c>
     </row>
   </sheetData>
